--- a/server/data/licc_members_database.xlsx
+++ b/server/data/licc_members_database.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="78">
   <si>
     <t>Member ID</t>
   </si>
@@ -38,9 +38,39 @@
     <t>Alt Phone</t>
   </si>
   <si>
+    <t>DOB</t>
+  </si>
+  <si>
     <t>Created At</t>
   </si>
   <si>
+    <t>MEM-646751</t>
+  </si>
+  <si>
+    <t>Solomon</t>
+  </si>
+  <si>
+    <t>Adeleke</t>
+  </si>
+  <si>
+    <t>Software Engineer / IT Professional</t>
+  </si>
+  <si>
+    <t>30-39</t>
+  </si>
+  <si>
+    <t>+2348165413816</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>25 Jan</t>
+  </si>
+  <si>
+    <t>2026-10-07T09:50:46.751Z</t>
+  </si>
+  <si>
     <t>Showcase ID</t>
   </si>
   <si>
@@ -141,9 +171,6 @@
   </si>
   <si>
     <t>+2348033333331</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>Overall Leadership, Fellowship Vision &amp; Spiritual Oversight</t>
@@ -612,7 +639,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -620,10 +647,11 @@
     <col min="4" max="4" width="25" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="7" width="20" customWidth="1"/>
-    <col min="8" max="8" width="24" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -647,6 +675,38 @@
       </c>
       <c r="H1" s="1" t="s">
         <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -673,34 +733,34 @@
   <sheetData>
     <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>7</v>
-      </c>
       <c r="J1" s="1" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -722,36 +782,36 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -779,34 +839,34 @@
   <sheetData>
     <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -831,45 +891,45 @@
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="B2" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="E2" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="F2" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -877,22 +937,22 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="C3" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D3" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="E3" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="F3" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -900,22 +960,22 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="B4" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="D4" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="E4" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="F4" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="G4">
         <v>3</v>
@@ -923,22 +983,22 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="D5" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="E5" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="F5" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="G5">
         <v>4</v>
@@ -946,22 +1006,22 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="D6" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="E6" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="F6" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -969,22 +1029,22 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="B7" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="C7" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="D7" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="E7" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="F7" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="G7">
         <v>6</v>
